--- a/clientes_para_importar_oct_2026.xlsx
+++ b/clientes_para_importar_oct_2026.xlsx
@@ -397,7 +397,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J38"/>
+  <cols>
+    <col min="1" max="1" width="38.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="70.83203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="100.83203125" customWidth="1"/>
+    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1487,9 +1499,137 @@
         <v/>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>REBECA ARROYO</v>
+      </c>
+      <c r="B35" t="str">
+        <v>74997227</v>
+      </c>
+      <c r="C35" t="str">
+        <v>919478260</v>
+      </c>
+      <c r="D35" t="str">
+        <v>JR. HUANTA</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Plan b?sico 250 Mbps</v>
+      </c>
+      <c r="F35">
+        <v>50</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>2PM-5PM</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Fecha no indicada; se usan los valores provisionales acordados.</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>BERTHA IMELDA ALACUTI GOYCOCHEA</v>
+      </c>
+      <c r="B36" t="str">
+        <v>47546647</v>
+      </c>
+      <c r="C36" t="str">
+        <v>928505034</v>
+      </c>
+      <c r="D36" t="str">
+        <v>MZ C LT 01 JIRON ICA</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Plan b?sico 250 Mbps</v>
+      </c>
+      <c r="F36">
+        <v>50</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>9AM-12PM</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Referencia: al costado del local comunal Valle del Triunfo. Fecha y mensualidad no indicadas; mensualidad provisional.</v>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>ORONCOY CASO KENYE EDILBERTO</v>
+      </c>
+      <c r="B37" t="str">
+        <v>4806781</v>
+      </c>
+      <c r="C37" t="str">
+        <v>900743707</v>
+      </c>
+      <c r="D37" t="str">
+        <v>MZ E LT 7 ASOC EL MIRADOR DEL SECTOR OESTE</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Plan b?sico 250 Mbps</v>
+      </c>
+      <c r="F37">
+        <v>50</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v>Sin fecha, plan ni mensualidad expl?citos; se usan valores provisionales.</v>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>JUAN BRYAN TACSA ROLDAN</v>
+      </c>
+      <c r="B38" t="str">
+        <v>76168375</v>
+      </c>
+      <c r="C38" t="str">
+        <v>958989485</v>
+      </c>
+      <c r="D38" t="str">
+        <v>LAS PLANICIES MZ W LTE 29</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Plan b?sico 250 Mbps</v>
+      </c>
+      <c r="F38">
+        <v>50</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>2PM-5PM</v>
+      </c>
+      <c r="I38" t="str">
+        <v>El texto indica instalaci?n entre 2PM y 5PM; plan y mensualidad provisionales.</v>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J38"/>
   </ignoredErrors>
 </worksheet>
 </file>